--- a/01_Processing/02_Quantification/c_data/quantification.xlsx
+++ b/01_Processing/02_Quantification/c_data/quantification.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7851" uniqueCount="7164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7797" uniqueCount="7129">
   <si>
     <t>sheet</t>
   </si>
@@ -130,13 +130,13 @@
     <t>prop_observed</t>
   </si>
   <si>
-    <t>Share of samples in which the protein was observed.</t>
+    <t>Share of the protein's precursor-by-biopsy values that were observed rather than modelled from the detection curve.</t>
   </si>
   <si>
     <t>sample_id</t>
   </si>
   <si>
-    <t>One biopsy: subject_timepoint.</t>
+    <t>One biopsy: person and time point, e.g. S03_T1.</t>
   </si>
   <si>
     <t>subject</t>
@@ -148,7 +148,7 @@
     <t>group</t>
   </si>
   <si>
-    <t>Group the row belongs to: HR or LR, or C1 or C2 in a proteome grouping.</t>
+    <t>HR (higher responder) or LR (lower responder).</t>
   </si>
   <si>
     <t>timepoint</t>
@@ -160,7 +160,7 @@
     <t>blood</t>
   </si>
   <si>
-    <t>Blood index (HBB and HBA1 against the sample median).</t>
+    <t>Blood index: the biopsy's mean log2 HBB and HBA1 from limpa, centred on the mean biopsy.</t>
   </si>
   <si>
     <t>class</t>
@@ -21115,228 +21115,153 @@
     <t>2c11f4485620b8319afe4056f618ec79</t>
   </si>
   <si>
-    <t>BiocGenerics</t>
-  </si>
-  <si>
-    <t>0.58.0</t>
+    <t>BiocManager</t>
+  </si>
+  <si>
+    <t>1.30.27</t>
+  </si>
+  <si>
+    <t>CRAN (R 4.6.0)</t>
+  </si>
+  <si>
+    <t>bit</t>
+  </si>
+  <si>
+    <t>4.6.0</t>
+  </si>
+  <si>
+    <t>bit64</t>
+  </si>
+  <si>
+    <t>4.8.0</t>
+  </si>
+  <si>
+    <t>cli</t>
+  </si>
+  <si>
+    <t>3.6.6</t>
+  </si>
+  <si>
+    <t>crayon</t>
+  </si>
+  <si>
+    <t>1.5.3</t>
+  </si>
+  <si>
+    <t>data.table</t>
+  </si>
+  <si>
+    <t>1.18.4</t>
+  </si>
+  <si>
+    <t>digest</t>
+  </si>
+  <si>
+    <t>0.6.39</t>
+  </si>
+  <si>
+    <t>dplyr</t>
+  </si>
+  <si>
+    <t>1.2.1</t>
+  </si>
+  <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
+    <t>farver</t>
+  </si>
+  <si>
+    <t>2.1.2</t>
+  </si>
+  <si>
+    <t>fastmap</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
+    <t>generics</t>
+  </si>
+  <si>
+    <t>0.1.4</t>
+  </si>
+  <si>
+    <t>ggplot2</t>
+  </si>
+  <si>
+    <t>4.0.3</t>
+  </si>
+  <si>
+    <t>glue</t>
+  </si>
+  <si>
+    <t>1.8.1</t>
+  </si>
+  <si>
+    <t>gtable</t>
+  </si>
+  <si>
+    <t>0.3.6</t>
+  </si>
+  <si>
+    <t>here</t>
+  </si>
+  <si>
+    <t>1.0.2</t>
+  </si>
+  <si>
+    <t>hms</t>
+  </si>
+  <si>
+    <t>1.1.4</t>
+  </si>
+  <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
+    <t>labeling</t>
+  </si>
+  <si>
+    <t>0.4.3</t>
+  </si>
+  <si>
+    <t>lifecycle</t>
+  </si>
+  <si>
+    <t>limma</t>
+  </si>
+  <si>
+    <t>3.68.1</t>
   </si>
   <si>
     <t>Bioconductor 3.23 (R 4.6.0)</t>
   </si>
   <si>
-    <t>BiocManager</t>
-  </si>
-  <si>
-    <t>1.30.27</t>
-  </si>
-  <si>
-    <t>CRAN (R 4.6.0)</t>
-  </si>
-  <si>
-    <t>bit</t>
-  </si>
-  <si>
-    <t>4.6.0</t>
-  </si>
-  <si>
-    <t>bit64</t>
-  </si>
-  <si>
-    <t>4.8.0</t>
-  </si>
-  <si>
-    <t>circlize</t>
-  </si>
-  <si>
-    <t>0.4.18</t>
-  </si>
-  <si>
-    <t>cli</t>
-  </si>
-  <si>
-    <t>3.6.6</t>
-  </si>
-  <si>
-    <t>clue</t>
-  </si>
-  <si>
-    <t>0.3-68</t>
-  </si>
-  <si>
-    <t>cluster</t>
-  </si>
-  <si>
-    <t>2.1.8.2</t>
-  </si>
-  <si>
-    <t>codetools</t>
-  </si>
-  <si>
-    <t>0.2-20</t>
-  </si>
-  <si>
-    <t>colorspace</t>
-  </si>
-  <si>
-    <t>2.1-2</t>
-  </si>
-  <si>
-    <t>ComplexHeatmap</t>
-  </si>
-  <si>
-    <t>2.28.0</t>
-  </si>
-  <si>
-    <t>crayon</t>
-  </si>
-  <si>
-    <t>1.5.3</t>
-  </si>
-  <si>
-    <t>data.table</t>
-  </si>
-  <si>
-    <t>1.18.4</t>
-  </si>
-  <si>
-    <t>digest</t>
-  </si>
-  <si>
-    <t>0.6.39</t>
-  </si>
-  <si>
-    <t>doParallel</t>
-  </si>
-  <si>
-    <t>1.0.17</t>
-  </si>
-  <si>
-    <t>dplyr</t>
-  </si>
-  <si>
-    <t>1.2.1</t>
-  </si>
-  <si>
-    <t>evaluate</t>
-  </si>
-  <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
-    <t>farver</t>
-  </si>
-  <si>
-    <t>2.1.2</t>
-  </si>
-  <si>
-    <t>fastmap</t>
-  </si>
-  <si>
-    <t>1.2.0</t>
-  </si>
-  <si>
-    <t>foreach</t>
-  </si>
-  <si>
-    <t>1.5.2</t>
-  </si>
-  <si>
-    <t>generics</t>
-  </si>
-  <si>
-    <t>0.1.4</t>
-  </si>
-  <si>
-    <t>GetoptLong</t>
-  </si>
-  <si>
-    <t>1.1.1</t>
-  </si>
-  <si>
-    <t>ggplot2</t>
-  </si>
-  <si>
-    <t>4.0.3</t>
-  </si>
-  <si>
-    <t>GlobalOptions</t>
-  </si>
-  <si>
-    <t>glue</t>
-  </si>
-  <si>
-    <t>1.8.1</t>
-  </si>
-  <si>
-    <t>gtable</t>
-  </si>
-  <si>
-    <t>0.3.6</t>
-  </si>
-  <si>
-    <t>here</t>
-  </si>
-  <si>
-    <t>1.0.2</t>
-  </si>
-  <si>
-    <t>hms</t>
-  </si>
-  <si>
-    <t>1.1.4</t>
-  </si>
-  <si>
-    <t>htmltools</t>
-  </si>
-  <si>
-    <t>0.5.9</t>
-  </si>
-  <si>
-    <t>htmlwidgets</t>
-  </si>
-  <si>
-    <t>1.6.4</t>
-  </si>
-  <si>
-    <t>IRanges</t>
-  </si>
-  <si>
-    <t>2.46.0</t>
-  </si>
-  <si>
-    <t>iterators</t>
-  </si>
-  <si>
-    <t>1.0.14</t>
-  </si>
-  <si>
-    <t>jsonlite</t>
-  </si>
-  <si>
-    <t>2.0.0</t>
-  </si>
-  <si>
-    <t>knitr</t>
-  </si>
-  <si>
-    <t>1.51</t>
-  </si>
-  <si>
-    <t>labeling</t>
-  </si>
-  <si>
-    <t>0.4.3</t>
-  </si>
-  <si>
-    <t>lifecycle</t>
-  </si>
-  <si>
-    <t>limma</t>
-  </si>
-  <si>
-    <t>3.68.1</t>
-  </si>
-  <si>
     <t>limpa</t>
   </si>
   <si>
@@ -21349,12 +21274,6 @@
     <t>2.0.5</t>
   </si>
   <si>
-    <t>matrixStats</t>
-  </si>
-  <si>
-    <t>1.5.0</t>
-  </si>
-  <si>
     <t>otel</t>
   </si>
   <si>
@@ -21373,12 +21292,6 @@
     <t>2.0.3</t>
   </si>
   <si>
-    <t>png</t>
-  </si>
-  <si>
-    <t>0.1-9</t>
-  </si>
-  <si>
     <t>R6</t>
   </si>
   <si>
@@ -21403,12 +21316,6 @@
     <t>1.2.3</t>
   </si>
   <si>
-    <t>rjson</t>
-  </si>
-  <si>
-    <t>0.2.23</t>
-  </si>
-  <si>
     <t>rlang</t>
   </si>
   <si>
@@ -21430,12 +21337,6 @@
     <t>2.1.1</t>
   </si>
   <si>
-    <t>S4Vectors</t>
-  </si>
-  <si>
-    <t>0.50.0</t>
-  </si>
-  <si>
     <t>S7</t>
   </si>
   <si>
@@ -21452,12 +21353,6 @@
   </si>
   <si>
     <t>1.2.4</t>
-  </si>
-  <si>
-    <t>shape</t>
-  </si>
-  <si>
-    <t>1.4.6.1</t>
   </si>
   <si>
     <t>statmod</t>
@@ -21947,7 +21842,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -21980,103 +21875,103 @@
         <v>7034</v>
       </c>
       <c r="C3" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>7035</v>
+      </c>
+      <c r="B4" t="s">
         <v>7036</v>
       </c>
-      <c r="B4" t="s">
-        <v>7037</v>
-      </c>
       <c r="C4" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>7037</v>
+      </c>
+      <c r="B5" t="s">
         <v>7038</v>
       </c>
-      <c r="B5" t="s">
-        <v>7039</v>
-      </c>
       <c r="C5" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>7039</v>
+      </c>
+      <c r="B6" t="s">
         <v>7040</v>
       </c>
-      <c r="B6" t="s">
-        <v>7041</v>
-      </c>
       <c r="C6" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>7041</v>
+      </c>
+      <c r="B7" t="s">
         <v>7042</v>
       </c>
-      <c r="B7" t="s">
-        <v>7043</v>
-      </c>
       <c r="C7" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>7043</v>
+      </c>
+      <c r="B8" t="s">
         <v>7044</v>
       </c>
-      <c r="B8" t="s">
-        <v>7045</v>
-      </c>
       <c r="C8" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>7045</v>
+      </c>
+      <c r="B9" t="s">
         <v>7046</v>
       </c>
-      <c r="B9" t="s">
-        <v>7047</v>
-      </c>
       <c r="C9" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
+        <v>7047</v>
+      </c>
+      <c r="B10" t="s">
         <v>7048</v>
       </c>
-      <c r="B10" t="s">
-        <v>7049</v>
-      </c>
       <c r="C10" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
+        <v>7049</v>
+      </c>
+      <c r="B11" t="s">
         <v>7050</v>
       </c>
-      <c r="B11" t="s">
-        <v>7051</v>
-      </c>
       <c r="C11" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
+        <v>7051</v>
+      </c>
+      <c r="B12" t="s">
         <v>7052</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7053</v>
       </c>
       <c r="C12" t="s">
         <v>7032</v>
@@ -22084,145 +21979,145 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
+        <v>7053</v>
+      </c>
+      <c r="B13" t="s">
         <v>7054</v>
       </c>
-      <c r="B13" t="s">
-        <v>7055</v>
-      </c>
       <c r="C13" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>7055</v>
+      </c>
+      <c r="B14" t="s">
         <v>7056</v>
       </c>
-      <c r="B14" t="s">
-        <v>7057</v>
-      </c>
       <c r="C14" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>7057</v>
+      </c>
+      <c r="B15" t="s">
         <v>7058</v>
       </c>
-      <c r="B15" t="s">
-        <v>7059</v>
-      </c>
       <c r="C15" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
+        <v>7059</v>
+      </c>
+      <c r="B16" t="s">
         <v>7060</v>
       </c>
-      <c r="B16" t="s">
-        <v>7061</v>
-      </c>
       <c r="C16" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
+        <v>7061</v>
+      </c>
+      <c r="B17" t="s">
         <v>7062</v>
       </c>
-      <c r="B17" t="s">
-        <v>7063</v>
-      </c>
       <c r="C17" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>7063</v>
+      </c>
+      <c r="B18" t="s">
         <v>7064</v>
       </c>
-      <c r="B18" t="s">
-        <v>7065</v>
-      </c>
       <c r="C18" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>7065</v>
+      </c>
+      <c r="B19" t="s">
         <v>7066</v>
       </c>
-      <c r="B19" t="s">
-        <v>7067</v>
-      </c>
       <c r="C19" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>7067</v>
+      </c>
+      <c r="B20" t="s">
         <v>7068</v>
       </c>
-      <c r="B20" t="s">
-        <v>7069</v>
-      </c>
       <c r="C20" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
+        <v>7069</v>
+      </c>
+      <c r="B21" t="s">
         <v>7070</v>
       </c>
-      <c r="B21" t="s">
-        <v>7071</v>
-      </c>
       <c r="C21" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
+        <v>7071</v>
+      </c>
+      <c r="B22" t="s">
         <v>7072</v>
       </c>
-      <c r="B22" t="s">
-        <v>7073</v>
-      </c>
       <c r="C22" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
+        <v>7073</v>
+      </c>
+      <c r="B23" t="s">
         <v>7074</v>
       </c>
-      <c r="B23" t="s">
-        <v>7075</v>
-      </c>
       <c r="C23" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>7076</v>
+        <v>7075</v>
       </c>
       <c r="B24" t="s">
-        <v>7077</v>
+        <v>7048</v>
       </c>
       <c r="C24" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>7076</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7077</v>
+      </c>
+      <c r="C25" t="s">
         <v>7078</v>
-      </c>
-      <c r="B25" t="s">
-        <v>7073</v>
-      </c>
-      <c r="C25" t="s">
-        <v>7035</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -22233,7 +22128,7 @@
         <v>7080</v>
       </c>
       <c r="C26" t="s">
-        <v>7035</v>
+        <v>7078</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -22244,7 +22139,7 @@
         <v>7082</v>
       </c>
       <c r="C27" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -22255,7 +22150,7 @@
         <v>7084</v>
       </c>
       <c r="C28" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -22266,7 +22161,7 @@
         <v>7086</v>
       </c>
       <c r="C29" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -22277,7 +22172,7 @@
         <v>7088</v>
       </c>
       <c r="C30" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -22288,7 +22183,7 @@
         <v>7090</v>
       </c>
       <c r="C31" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -22310,7 +22205,7 @@
         <v>7094</v>
       </c>
       <c r="C33" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -22321,7 +22216,7 @@
         <v>7096</v>
       </c>
       <c r="C34" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -22332,37 +22227,37 @@
         <v>7098</v>
       </c>
       <c r="C35" t="s">
-        <v>7035</v>
+        <v>7099</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>7099</v>
+        <v>7100</v>
       </c>
       <c r="B36" t="s">
-        <v>7100</v>
+        <v>7101</v>
       </c>
       <c r="C36" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>7101</v>
+        <v>7102</v>
       </c>
       <c r="B37" t="s">
-        <v>7065</v>
+        <v>7103</v>
       </c>
       <c r="C37" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>7102</v>
+        <v>7104</v>
       </c>
       <c r="B38" t="s">
-        <v>7103</v>
+        <v>7105</v>
       </c>
       <c r="C38" t="s">
         <v>7032</v>
@@ -22370,10 +22265,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>7104</v>
+        <v>7106</v>
       </c>
       <c r="B39" t="s">
-        <v>7105</v>
+        <v>7107</v>
       </c>
       <c r="C39" t="s">
         <v>7032</v>
@@ -22381,321 +22276,123 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>7106</v>
+        <v>7108</v>
       </c>
       <c r="B40" t="s">
-        <v>7107</v>
+        <v>7109</v>
       </c>
       <c r="C40" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>7108</v>
+        <v>7110</v>
       </c>
       <c r="B41" t="s">
-        <v>7109</v>
+        <v>7111</v>
       </c>
       <c r="C41" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>7110</v>
+        <v>7112</v>
       </c>
       <c r="B42" t="s">
-        <v>7111</v>
+        <v>7113</v>
       </c>
       <c r="C42" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>7112</v>
+        <v>7114</v>
       </c>
       <c r="B43" t="s">
-        <v>7113</v>
+        <v>7046</v>
       </c>
       <c r="C43" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>7114</v>
+        <v>7115</v>
       </c>
       <c r="B44" t="s">
-        <v>7115</v>
+        <v>7116</v>
       </c>
       <c r="C44" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>7116</v>
+        <v>7117</v>
       </c>
       <c r="B45" t="s">
-        <v>7117</v>
+        <v>7118</v>
       </c>
       <c r="C45" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>7118</v>
+        <v>7119</v>
       </c>
       <c r="B46" t="s">
-        <v>7119</v>
+        <v>7120</v>
       </c>
       <c r="C46" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>7120</v>
+        <v>7121</v>
       </c>
       <c r="B47" t="s">
-        <v>7121</v>
+        <v>7122</v>
       </c>
       <c r="C47" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>7122</v>
+        <v>7123</v>
       </c>
       <c r="B48" t="s">
-        <v>7123</v>
+        <v>7124</v>
       </c>
       <c r="C48" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>7124</v>
+        <v>7125</v>
       </c>
       <c r="B49" t="s">
-        <v>7125</v>
+        <v>7126</v>
       </c>
       <c r="C49" t="s">
-        <v>7035</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>7126</v>
+        <v>7127</v>
       </c>
       <c r="B50" t="s">
-        <v>7127</v>
+        <v>7128</v>
       </c>
       <c r="C50" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>7128</v>
-      </c>
-      <c r="B51" t="s">
-        <v>7129</v>
-      </c>
-      <c r="C51" t="s">
-        <v>7130</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
-        <v>7131</v>
-      </c>
-      <c r="B52" t="s">
-        <v>7132</v>
-      </c>
-      <c r="C52" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
-        <v>7133</v>
-      </c>
-      <c r="B53" t="s">
-        <v>7134</v>
-      </c>
-      <c r="C53" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
-        <v>7135</v>
-      </c>
-      <c r="B54" t="s">
-        <v>7136</v>
-      </c>
-      <c r="C54" t="s">
         <v>7032</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" t="s">
-        <v>7137</v>
-      </c>
-      <c r="B55" t="s">
-        <v>7138</v>
-      </c>
-      <c r="C55" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
-        <v>7139</v>
-      </c>
-      <c r="B56" t="s">
-        <v>7140</v>
-      </c>
-      <c r="C56" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" t="s">
-        <v>7141</v>
-      </c>
-      <c r="B57" t="s">
-        <v>7142</v>
-      </c>
-      <c r="C57" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
-        <v>7143</v>
-      </c>
-      <c r="B58" t="s">
-        <v>7144</v>
-      </c>
-      <c r="C58" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" t="s">
-        <v>7145</v>
-      </c>
-      <c r="B59" t="s">
-        <v>7146</v>
-      </c>
-      <c r="C59" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" t="s">
-        <v>7147</v>
-      </c>
-      <c r="B60" t="s">
-        <v>7148</v>
-      </c>
-      <c r="C60" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" t="s">
-        <v>7149</v>
-      </c>
-      <c r="B61" t="s">
-        <v>7063</v>
-      </c>
-      <c r="C61" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
-        <v>7150</v>
-      </c>
-      <c r="B62" t="s">
-        <v>7151</v>
-      </c>
-      <c r="C62" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>7152</v>
-      </c>
-      <c r="B63" t="s">
-        <v>7153</v>
-      </c>
-      <c r="C63" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
-        <v>7154</v>
-      </c>
-      <c r="B64" t="s">
-        <v>7155</v>
-      </c>
-      <c r="C64" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
-        <v>7156</v>
-      </c>
-      <c r="B65" t="s">
-        <v>7157</v>
-      </c>
-      <c r="C65" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>7158</v>
-      </c>
-      <c r="B66" t="s">
-        <v>7159</v>
-      </c>
-      <c r="C66" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
-        <v>7160</v>
-      </c>
-      <c r="B67" t="s">
-        <v>7161</v>
-      </c>
-      <c r="C67" t="s">
-        <v>7035</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" t="s">
-        <v>7162</v>
-      </c>
-      <c r="B68" t="s">
-        <v>7163</v>
-      </c>
-      <c r="C68" t="s">
-        <v>7035</v>
       </c>
     </row>
   </sheetData>

--- a/01_Processing/02_Quantification/c_data/quantification.xlsx
+++ b/01_Processing/02_Quantification/c_data/quantification.xlsx
@@ -124,7 +124,7 @@
     <t>n_precursors</t>
   </si>
   <si>
-    <t>Precursors detected (q ≤ 0.01) in the run or protein.</t>
+    <t>Precursors limpa used for the protein (NPrec).</t>
   </si>
   <si>
     <t>prop_observed</t>
